--- a/admin/template/purchase_apply_template.xlsx
+++ b/admin/template/purchase_apply_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2B4A09-A3A1-4B01-83B1-6DFAD85496E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC020C57-A77A-4D96-A223-3C402CF8298C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,12 +23,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>采购申请单</t>
   </si>
@@ -42,9 +45,6 @@
     <t>规格</t>
   </si>
   <si>
-    <t>价格</t>
-  </si>
-  <si>
     <t>用途</t>
   </si>
   <si>
@@ -143,6 +143,18 @@
   </si>
   <si>
     <t>合计（元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单价</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合计</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.cost}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -350,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -382,12 +394,48 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -402,30 +450,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -707,27 +731,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.75" customWidth="1"/>
-    <col min="2" max="2" width="12.125" customWidth="1"/>
+    <col min="2" max="2" width="3.25" customWidth="1"/>
     <col min="3" max="3" width="13.875" customWidth="1"/>
     <col min="4" max="4" width="9.25" customWidth="1"/>
-    <col min="6" max="6" width="26.625" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="24.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -735,119 +761,130 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="3" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="16"/>
+      <c r="B3" s="28"/>
       <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="54" x14ac:dyDescent="0.2">
+      <c r="A4" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>5</v>
+      <c r="E4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="54" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="6" t="s">
+    <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="E6" s="31"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="21" t="s">
         <v>11</v>
       </c>
+      <c r="B7" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="22" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+    <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.2">
+      <c r="A8" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D8" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="11" t="s">
+      <c r="E8" s="23"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="17" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="25"/>
-      <c r="F7" s="27" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="27" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="22" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
